--- a/Projets_complete.xlsx
+++ b/Projets_complete.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise/Dropbox/CV_en_ligne/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise/Dropbox/CV_en_ligne/site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9366DFD5-48B1-254D-B0F8-F6AD70095353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA18A30-08E1-E64A-841F-4FA68E5BF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="880" windowWidth="28040" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>Titre du projet</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>Abré Sonhaye-Ouye, M1, Sorbonne Paris North University (USPN)</t>
+  </si>
+  <si>
+    <t>Cadrage image</t>
+  </si>
+  <si>
+    <t>entière</t>
   </si>
 </sst>
 </file>
@@ -648,13 +654,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="23.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,8 +691,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" ht="380" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="6" customFormat="1" ht="380" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -715,8 +724,11 @@
         <v>51</v>
       </c>
       <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:10" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -748,7 +760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="C4" s="7" t="s">
         <v>27</v>
@@ -770,7 +782,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>42</v>
       </c>
@@ -795,8 +807,11 @@
       <c r="J5" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
@@ -824,7 +839,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -850,7 +865,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -860,7 +875,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -870,7 +885,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -880,7 +895,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -890,7 +905,7 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>

--- a/Projets_complete.xlsx
+++ b/Projets_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise/Dropbox/CV_en_ligne/site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA18A30-08E1-E64A-841F-4FA68E5BF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D29D5D1-41B9-374B-94BA-CB9BD46B4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="880" windowWidth="28040" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>Laboratoire d’Ethologie Expérimentale et Comparée (LEEC), Université Sorbonne Paris Nord</t>
   </si>
   <si>
-    <t>Funded by the « Appel à Projets de la Commission de la recherche USPN » (10k€)</t>
-  </si>
-  <si>
     <t>Lluìs Socias Martinez
 M. Cristina Lorenzi
 Malo Loubière</t>
@@ -93,9 +90,6 @@
   </si>
   <si>
     <t>Deutsches Primatenzentrum (German Primate Center), Göttingen</t>
-  </si>
-  <si>
-    <t>Funded by the Deutsche Forschungsgemeinschaft (DFG)</t>
   </si>
   <si>
     <t>Claudia Fichtel
@@ -206,26 +200,32 @@
 </t>
   </si>
   <si>
-    <t>Mana Mellin, M2, Sorbonne Paris North University (USPN)
-Alice Bonuccelli, M1, Université Caen-Normandie
-Alice Martret, L3, USPN</t>
+    <t>Cadrage image</t>
+  </si>
+  <si>
+    <t>entière</t>
+  </si>
+  <si>
+    <t>Appel à Projets de la Commission de la recherche USPN (10k€)</t>
+  </si>
+  <si>
+    <t>Deutsche Forschungsgemeinschaft (DFG)</t>
+  </si>
+  <si>
+    <t>Mana Mellin (M2), USPN
+Alice Bonuccelli (M1), Université Caen-Normandie
+Alice Martret (L3), USPN</t>
   </si>
   <si>
     <t>Alexandra Michiels, volunteer student
-Lilas Allard, M1, Institut Supérieur d’Agriculture (ISA)
-Miravo Randrianirinarisoa, M1, Université d’Antananarivo, Madagascar</t>
-  </si>
-  <si>
-    <t>Titouan Willer, M2, Sorbonne Paris North University (USPN)</t>
-  </si>
-  <si>
-    <t>Abré Sonhaye-Ouye, M1, Sorbonne Paris North University (USPN)</t>
-  </si>
-  <si>
-    <t>Cadrage image</t>
-  </si>
-  <si>
-    <t>entière</t>
+Lilas Allard (M1), Institut Supérieur d’Agriculture (ISA)
+Miravo Randrianirinarisoa (M1), Université d’Antananarivo, Madagascar</t>
+  </si>
+  <si>
+    <t>Titouan Willer (M2), USPN</t>
+  </si>
+  <si>
+    <t>Abré Sonhaye-Ouye (M1), USPN</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="6" customFormat="1" ht="380" customHeight="1" x14ac:dyDescent="0.2">
@@ -712,157 +712,157 @@
         <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
       <c r="C4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">

--- a/Projets_complete.xlsx
+++ b/Projets_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise/Dropbox/CV_en_ligne/site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D29D5D1-41B9-374B-94BA-CB9BD46B4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BBCDB8-951D-404C-AF8B-B4F0A8FA8720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="880" windowWidth="28040" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>Titre du projet</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>Abré Sonhaye-Ouye (M1), USPN</t>
+  </si>
+  <si>
+    <t>zebras.jpg</t>
   </si>
 </sst>
 </file>
@@ -762,6 +765,9 @@
     </row>
     <row r="4" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
+      <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="C4" s="7" t="s">
         <v>25</v>
       </c>
